--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5364-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5364-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6ACE1BA-3204-4F86-81AA-DDE8B68B6A4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F54A8E4-7F1E-42FD-97FC-539FC317299C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{2F44A059-840F-4663-93A0-13E3E20BE5A0}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A59C18B3-BC70-4494-8DC9-F5D8A6908898}"/>
   </bookViews>
   <sheets>
     <sheet name="5364-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1430,28 +1430,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D5E1AE6-BBF9-424F-9413-7CF20172C7EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F3CFC20-C393-4287-B69C-E613096B8BC6}">
   <dimension ref="A1:X37"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1485,7 +1484,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1521,7 +1520,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1573,7 +1572,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1641,7 +1640,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1713,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1785,7 +1784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1857,7 +1856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1929,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2001,7 +2000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2073,7 +2072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2145,7 +2144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2217,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2289,7 +2288,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2361,7 +2360,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="35">
         <v>2014</v>
       </c>
@@ -2433,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>2013</v>
       </c>
@@ -2505,7 +2504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="35">
         <v>2012</v>
       </c>
@@ -2577,7 +2576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2011</v>
       </c>
@@ -2649,7 +2648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="35">
         <v>2010</v>
       </c>
@@ -2721,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2009</v>
       </c>
@@ -2793,7 +2792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="35">
         <v>2008</v>
       </c>
@@ -2865,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2007</v>
       </c>
@@ -2937,7 +2936,7 @@
         <v>46.7</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="35">
         <v>2006</v>
       </c>
@@ -3009,7 +3008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2005</v>
       </c>
@@ -3081,7 +3080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="35">
         <v>2004</v>
       </c>
@@ -3153,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2003</v>
       </c>
@@ -3225,7 +3224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2002</v>
       </c>
@@ -3297,7 +3296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2001</v>
       </c>
@@ -3369,7 +3368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2000</v>
       </c>
@@ -3441,7 +3440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1999</v>
       </c>
@@ -3513,7 +3512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>1998</v>
       </c>
@@ -3585,7 +3584,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1997</v>
       </c>
@@ -3657,7 +3656,7 @@
         <v>8.2100000000000009</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>1996</v>
       </c>
@@ -3729,7 +3728,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1995</v>
       </c>
@@ -3801,7 +3800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>1994</v>
       </c>
@@ -3873,7 +3872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1993</v>
       </c>
@@ -3945,7 +3944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35" t="s">
         <v>34</v>
       </c>
